--- a/Aml.BOM.Import.Shared/Resources/SampleBOMFile/Proposed Sage Upload Template_r7.xlsx
+++ b/Aml.BOM.Import.Shared/Resources/SampleBOMFile/Proposed Sage Upload Template_r7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Infospring Projects\Aml.BOM.Import\Aml.BOM.Import.Shared\Resources\SampleBOMFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70429EC-E287-4565-8131-BADCB77F3B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D41214E-1AD1-4967-8A39-859FADABFE79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{56B43026-45B4-47E7-A4A0-0E830622CF7E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{56B43026-45B4-47E7-A4A0-0E830622CF7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Phantom" sheetId="3" r:id="rId1"/>
@@ -21,16 +21,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -10083,7 +10073,7 @@
         <v>252</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>230</v>
